--- a/Data/FlightPlan/FPL_30SEP26.xlsx
+++ b/Data/FlightPlan/FPL_30SEP26.xlsx
@@ -326,6 +326,15 @@
     <t>22:36</t>
   </si>
   <si>
+    <t>KIX</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
     <t>VN-A522</t>
   </si>
   <si>
@@ -491,15 +500,6 @@
     <t>20:47</t>
   </si>
   <si>
-    <t>KIX</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
     <t>VN-A529</t>
   </si>
   <si>
@@ -1013,6 +1013,9 @@
     <t>02:10</t>
   </si>
   <si>
+    <t>02:26</t>
+  </si>
+  <si>
     <t>03:00</t>
   </si>
   <si>
@@ -1268,7 +1271,7 @@
     <t>22:30</t>
   </si>
   <si>
-    <t>01:25</t>
+    <t>01:36</t>
   </si>
   <si>
     <t>03:05</t>
@@ -1310,6 +1313,9 @@
     <t>22:17</t>
   </si>
   <si>
+    <t>00:38</t>
+  </si>
+  <si>
     <t>VN-A646</t>
   </si>
   <si>
@@ -1334,6 +1340,9 @@
     <t>20:29</t>
   </si>
   <si>
+    <t>00:00</t>
+  </si>
+  <si>
     <t>VN-A649</t>
   </si>
   <si>
@@ -1913,7 +1922,7 @@
     <t>Total Record(s): 369</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 30, 2026 22:36</t>
+    <t xml:space="preserve">Generated on  Sep 30, 2026 23:02</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3351,77 +3360,75 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
+      <c t="s" r="A35" s="6">
+        <v>59</v>
+      </c>
+      <c r="B35" s="7">
+        <v>828</v>
+      </c>
+      <c t="s" r="C35" s="7">
+        <v>14</v>
+      </c>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
+      <c t="s" r="E35" s="7">
+        <v>88</v>
+      </c>
+      <c r="F35" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G35" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H35" s="8">
+        <v>105</v>
+      </c>
+      <c t="s" r="I35" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J35" s="7">
+        <v>107</v>
+      </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c t="s" r="A36" s="6">
-        <v>13</v>
-      </c>
-      <c r="B36" s="7">
-        <v>807</v>
-      </c>
-      <c t="s" r="C36" s="7">
-        <v>14</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="7"/>
-      <c t="s" r="E36" s="7">
-        <v>105</v>
-      </c>
-      <c r="F36" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G36" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H36" s="8">
-        <v>106</v>
-      </c>
-      <c t="s" r="I36" s="7">
-        <v>107</v>
-      </c>
-      <c t="s" r="J36" s="7">
-        <v>108</v>
-      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
-      <c t="s" r="M36" s="7">
-        <v>109</v>
-      </c>
+      <c r="M36" s="7"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c t="s" r="A37" s="6">
         <v>13</v>
       </c>
       <c r="B37" s="7">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c t="s" r="C37" s="7">
         <v>14</v>
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c t="s" r="I37" s="7">
         <v>110</v>
@@ -3440,33 +3447,31 @@
         <v>13</v>
       </c>
       <c r="B38" s="7">
-        <v>146</v>
+        <v>800</v>
       </c>
       <c t="s" r="C38" s="7">
         <v>14</v>
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>113</v>
-      </c>
-      <c t="s" r="K38" s="7">
         <v>114</v>
       </c>
+      <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
         <v>115</v>
@@ -3477,121 +3482,123 @@
         <v>13</v>
       </c>
       <c r="B39" s="7">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c t="s" r="C39" s="7">
         <v>14</v>
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H39" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H39" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I39" s="7">
+        <v>115</v>
+      </c>
+      <c t="s" r="J39" s="7">
         <v>116</v>
       </c>
-      <c t="s" r="J39" s="7">
+      <c t="s" r="K39" s="7">
         <v>117</v>
-      </c>
-      <c t="s" r="K39" s="7">
-        <v>118</v>
       </c>
       <c r="L39" s="7"/>
       <c t="s" r="M39" s="7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c t="s" r="A40" s="6">
+        <v>13</v>
+      </c>
+      <c r="B40" s="7">
+        <v>161</v>
+      </c>
+      <c t="s" r="C40" s="7">
+        <v>14</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c t="s" r="E40" s="7">
+        <v>108</v>
+      </c>
+      <c r="F40" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G40" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H40" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I40" s="7">
         <v>119</v>
       </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
+      <c t="s" r="J40" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="K40" s="7">
+        <v>121</v>
+      </c>
       <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
+      <c t="s" r="M40" s="7">
+        <v>122</v>
+      </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c t="s" r="A41" s="6">
-        <v>13</v>
-      </c>
-      <c r="B41" s="7">
-        <v>350</v>
-      </c>
-      <c t="s" r="C41" s="7">
-        <v>14</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c t="s" r="E41" s="7">
-        <v>120</v>
-      </c>
-      <c r="F41" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G41" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H41" s="8">
-        <v>121</v>
-      </c>
-      <c t="s" r="I41" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="J41" s="7">
-        <v>123</v>
-      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
-      <c t="s" r="M41" s="7">
-        <v>124</v>
-      </c>
+      <c r="M41" s="7"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c t="s" r="A42" s="6">
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>740</v>
+        <v>350</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c t="s" r="I42" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c t="s" r="M42" s="7">
-        <v>79</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -3599,34 +3606,34 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>227</v>
+        <v>740</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
+        <v>124</v>
+      </c>
+      <c t="s" r="H43" s="8">
         <v>69</v>
       </c>
-      <c t="s" r="H43" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I43" s="7">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>127</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -3634,34 +3641,34 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c t="s" r="C44" s="7">
         <v>14</v>
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3669,29 +3676,29 @@
         <v>13</v>
       </c>
       <c r="B45" s="7">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c t="s" r="C45" s="7">
         <v>14</v>
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H45" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H45" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I45" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3704,109 +3711,109 @@
         <v>13</v>
       </c>
       <c r="B46" s="7">
-        <v>822</v>
+        <v>159</v>
       </c>
       <c t="s" r="C46" s="7">
         <v>14</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="H46" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I46" s="7">
         <v>133</v>
-      </c>
-      <c t="s" r="I46" s="7">
-        <v>26</v>
       </c>
       <c t="s" r="J46" s="7">
         <v>134</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
+      <c t="s" r="M46" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
+      <c t="s" r="A47" s="6">
+        <v>13</v>
+      </c>
+      <c r="B47" s="7">
+        <v>822</v>
+      </c>
+      <c t="s" r="C47" s="7">
+        <v>14</v>
+      </c>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
+      <c t="s" r="E47" s="7">
+        <v>123</v>
+      </c>
+      <c r="F47" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G47" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H47" s="8">
+        <v>136</v>
+      </c>
+      <c t="s" r="I47" s="7">
+        <v>26</v>
+      </c>
+      <c t="s" r="J47" s="7">
+        <v>137</v>
+      </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c t="s" r="A48" s="6">
-        <v>13</v>
-      </c>
-      <c r="B48" s="7">
-        <v>260</v>
-      </c>
-      <c t="s" r="C48" s="7">
-        <v>14</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c t="s" r="E48" s="7">
-        <v>135</v>
-      </c>
-      <c r="F48" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G48" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H48" s="8">
-        <v>136</v>
-      </c>
-      <c t="s" r="I48" s="7">
-        <v>61</v>
-      </c>
-      <c t="s" r="J48" s="7">
-        <v>137</v>
-      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
-      <c t="s" r="M48" s="7">
-        <v>138</v>
-      </c>
+      <c r="M48" s="7"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c t="s" r="A49" s="6">
         <v>13</v>
       </c>
       <c r="B49" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="C49" s="7">
         <v>14</v>
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>140</v>
@@ -3822,23 +3829,23 @@
         <v>13</v>
       </c>
       <c r="B50" s="7">
-        <v>1602</v>
+        <v>261</v>
       </c>
       <c t="s" r="C50" s="7">
         <v>14</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c t="s" r="I50" s="7">
         <v>142</v>
@@ -3857,26 +3864,26 @@
         <v>13</v>
       </c>
       <c r="B51" s="7">
-        <v>5512</v>
+        <v>1602</v>
       </c>
       <c t="s" r="C51" s="7">
         <v>14</v>
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H51" s="8">
         <v>38</v>
       </c>
-      <c t="s" r="H51" s="8">
+      <c t="s" r="I51" s="7">
         <v>145</v>
-      </c>
-      <c t="s" r="I51" s="7">
-        <v>80</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>146</v>
@@ -3892,121 +3899,119 @@
         <v>13</v>
       </c>
       <c r="B52" s="7">
-        <v>5513</v>
+        <v>5512</v>
       </c>
       <c t="s" r="C52" s="7">
         <v>14</v>
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
+      <c t="s" r="A53" s="6">
+        <v>13</v>
+      </c>
+      <c r="B53" s="7">
+        <v>5513</v>
+      </c>
+      <c t="s" r="C53" s="7">
+        <v>14</v>
+      </c>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
+      <c t="s" r="E53" s="7">
+        <v>138</v>
+      </c>
+      <c r="F53" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G53" s="8">
+        <v>148</v>
+      </c>
+      <c t="s" r="H53" s="8">
+        <v>38</v>
+      </c>
+      <c t="s" r="I53" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J53" s="7">
+        <v>151</v>
+      </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
+      <c t="s" r="M53" s="7">
+        <v>152</v>
+      </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c t="s" r="A54" s="6">
-        <v>13</v>
-      </c>
-      <c r="B54" s="7">
-        <v>274</v>
-      </c>
-      <c t="s" r="C54" s="7">
-        <v>14</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c t="s" r="E54" s="7">
-        <v>150</v>
-      </c>
-      <c r="F54" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G54" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H54" s="8">
-        <v>48</v>
-      </c>
-      <c t="s" r="I54" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="J54" s="7">
-        <v>20</v>
-      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
-      <c t="s" r="M54" s="7">
-        <v>152</v>
-      </c>
+      <c r="M54" s="7"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c t="s" r="A55" s="6">
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="C55" s="7">
         <v>14</v>
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H55" s="8">
         <v>48</v>
       </c>
-      <c t="s" r="H55" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I55" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>65</v>
-      </c>
-      <c t="s" r="K55" s="7">
-        <v>154</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c t="s" r="M55" s="7">
-        <v>97</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -4014,36 +4019,36 @@
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c t="s" r="C56" s="7">
         <v>14</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c t="s" r="K56" s="7">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>156</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -4051,32 +4056,32 @@
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="C57" s="7">
         <v>14</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H57" s="8">
         <v>69</v>
       </c>
-      <c t="s" r="H57" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I57" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="K57" s="7">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
@@ -4085,36 +4090,40 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B58" s="7">
-        <v>828</v>
+        <v>211</v>
       </c>
       <c t="s" r="C58" s="7">
         <v>14</v>
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c t="s" r="H58" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I58" s="7">
         <v>160</v>
       </c>
-      <c t="s" r="I58" s="7">
+      <c t="s" r="J58" s="7">
+        <v>116</v>
+      </c>
+      <c t="s" r="K58" s="7">
         <v>161</v>
       </c>
-      <c t="s" r="J58" s="7">
+      <c r="L58" s="7"/>
+      <c t="s" r="M58" s="7">
         <v>162</v>
       </c>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="6"/>
@@ -4149,7 +4158,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>29</v>
@@ -4225,13 +4234,13 @@
         <v>29</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>53</v>
       </c>
       <c t="s" r="K62" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
@@ -4277,7 +4286,7 @@
         <v>69</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>171</v>
@@ -4414,7 +4423,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="I68" s="7">
         <v>182</v>
@@ -4446,7 +4455,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>17</v>
@@ -4534,7 +4543,7 @@
         <v>69</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="I72" s="7">
         <v>191</v>
@@ -4566,7 +4575,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>17</v>
@@ -4575,7 +4584,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -4642,7 +4651,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>199</v>
@@ -4680,7 +4689,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4712,10 +4721,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4768,7 +4777,7 @@
         <v>205</v>
       </c>
       <c t="s" r="K79" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
@@ -4921,7 +4930,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>32</v>
@@ -4959,7 +4968,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -5064,7 +5073,7 @@
         <v>199</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -5108,7 +5117,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="I90" s="7">
         <v>27</v>
@@ -5140,7 +5149,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>29</v>
@@ -5149,7 +5158,7 @@
         <v>224</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -5181,7 +5190,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>93</v>
@@ -5256,10 +5265,10 @@
         <v>229</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="K94" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
@@ -5290,7 +5299,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>185</v>
@@ -5324,7 +5333,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c t="s" r="I96" s="7">
         <v>231</v>
@@ -5375,10 +5384,10 @@
         <v>233</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5413,7 +5422,7 @@
         <v>235</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5448,7 +5457,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5531,7 +5540,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5786,7 +5795,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>32</v>
@@ -5859,12 +5868,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5929,7 +5938,7 @@
         <v>246</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -6233,10 +6242,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>66</v>
@@ -6265,7 +6274,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>29</v>
@@ -6279,7 +6288,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6303,13 +6312,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>213</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -6354,13 +6363,13 @@
         <v>38</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>79</v>
       </c>
       <c t="s" r="K129" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
@@ -6464,7 +6473,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6629,7 +6638,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>44</v>
@@ -6667,7 +6676,7 @@
         <v>295</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6712,7 +6721,7 @@
         <v>297</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>18</v>
@@ -6817,7 +6826,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>83</v>
@@ -6898,7 +6907,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>17</v>
@@ -6907,7 +6916,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -7049,14 +7058,14 @@
         <v>312</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="K151" s="7">
         <v>312</v>
       </c>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -7092,7 +7101,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>17</v>
@@ -7136,12 +7145,12 @@
         <v>199</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>161</v>
+        <v>106</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7289,7 +7298,7 @@
         <v>315</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -7403,10 +7412,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>55</v>
@@ -7435,21 +7444,21 @@
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7483,7 +7492,9 @@
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c t="s" r="M165" s="7">
+        <v>334</v>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c t="s" r="A166" s="6">
@@ -7509,10 +7520,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7545,7 +7556,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7565,7 +7576,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7580,7 +7591,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7602,7 +7613,7 @@
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7617,7 +7628,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7632,12 +7643,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7652,7 +7663,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7667,14 +7678,14 @@
         <v>235</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="K171" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7689,7 +7700,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7701,7 +7712,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>83</v>
@@ -7724,7 +7735,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7759,7 +7770,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7771,7 +7782,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>304</v>
@@ -7781,7 +7792,7 @@
       </c>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7811,7 +7822,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7823,7 +7834,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>93</v>
@@ -7848,7 +7859,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7868,7 +7879,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7883,7 +7894,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7895,15 +7906,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7918,7 +7929,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7933,7 +7944,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7968,7 +7979,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7988,7 +7999,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -8003,7 +8014,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -8015,15 +8026,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -8038,7 +8049,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -8050,7 +8061,7 @@
         <v>219</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>167</v>
@@ -8058,7 +8069,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -8073,7 +8084,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -8108,7 +8119,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8128,7 +8139,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8143,7 +8154,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8155,15 +8166,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8193,7 +8204,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8202,7 +8213,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I188" s="7">
         <v>321</v>
@@ -8213,7 +8224,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8228,13 +8239,13 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>29</v>
@@ -8248,7 +8259,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8263,7 +8274,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8283,7 +8294,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8298,7 +8309,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8310,7 +8321,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>248</v>
@@ -8318,7 +8329,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8333,7 +8344,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8345,15 +8356,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8368,7 +8379,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8380,7 +8391,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>56</v>
@@ -8388,7 +8399,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8418,7 +8429,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8438,7 +8449,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8453,7 +8464,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8462,7 +8473,7 @@
         <v>176</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>282</v>
@@ -8488,13 +8499,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>176</v>
@@ -8523,7 +8534,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8532,13 +8543,13 @@
         <v>176</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -8558,13 +8569,13 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>176</v>
@@ -8573,12 +8584,12 @@
         <v>75</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8608,7 +8619,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8620,15 +8631,15 @@
         <v>219</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8643,7 +8654,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8655,7 +8666,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>242</v>
@@ -8663,7 +8674,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8678,7 +8689,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8698,7 +8709,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8713,7 +8724,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8728,12 +8739,12 @@
         <v>227</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8748,7 +8759,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8768,7 +8779,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8783,7 +8794,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8798,14 +8809,14 @@
         <v>23</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="K206" s="7">
         <v>101</v>
       </c>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8835,7 +8846,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8844,18 +8855,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c t="s" r="I208" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8870,13 +8881,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>29</v>
@@ -8890,7 +8901,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8905,7 +8916,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8914,20 +8925,20 @@
         <v>29</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>249</v>
       </c>
       <c t="s" r="K210" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8942,29 +8953,29 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="K211" s="7">
         <v>71</v>
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8994,7 +9005,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -9006,7 +9017,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>173</v>
@@ -9014,7 +9025,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -9029,7 +9040,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -9041,15 +9052,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -9064,7 +9075,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -9076,7 +9087,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>94</v>
@@ -9084,7 +9095,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9099,7 +9110,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9117,11 +9128,11 @@
         <v>307</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9136,7 +9147,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -9151,10 +9162,10 @@
         <v>52</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="K217" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
@@ -9173,7 +9184,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9185,17 +9196,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="K218" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9225,7 +9236,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9234,10 +9245,10 @@
         <v>176</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>178</v>
@@ -9260,13 +9271,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>176</v>
@@ -9295,7 +9306,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9307,7 +9318,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>98</v>
@@ -9315,7 +9326,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9330,7 +9341,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9345,14 +9356,14 @@
         <v>55</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="K223" s="7">
         <v>42</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9382,7 +9393,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9391,18 +9402,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>241</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9417,19 +9428,19 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>65</v>
@@ -9437,7 +9448,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9452,7 +9463,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9464,15 +9475,15 @@
         <v>38</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9487,7 +9498,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9499,15 +9510,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9537,7 +9548,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9557,7 +9568,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9572,7 +9583,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9587,12 +9598,12 @@
         <v>194</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9607,7 +9618,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9619,15 +9630,15 @@
         <v>219</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9642,7 +9653,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9662,7 +9673,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9677,7 +9688,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9686,10 +9697,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>183</v>
@@ -9697,7 +9708,7 @@
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9712,13 +9723,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>29</v>
@@ -9730,11 +9741,11 @@
         <v>102</v>
       </c>
       <c t="s" r="K235" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9749,7 +9760,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9758,20 +9769,20 @@
         <v>29</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>275</v>
       </c>
       <c t="s" r="K236" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9786,13 +9797,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>29</v>
@@ -9801,7 +9812,7 @@
         <v>333</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9834,7 +9845,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9846,7 +9857,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>328</v>
@@ -9854,7 +9865,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9869,7 +9880,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9884,12 +9895,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9904,7 +9915,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9939,7 +9950,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9954,7 +9965,7 @@
         <v>295</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9987,7 +9998,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9996,18 +10007,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -10022,13 +10033,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
@@ -10042,7 +10053,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -10057,7 +10068,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -10077,7 +10088,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -10092,7 +10103,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10101,10 +10112,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>248</v>
@@ -10120,34 +10131,34 @@
         <v>13</v>
       </c>
       <c t="s" r="B248" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10162,7 +10173,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10171,10 +10182,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>103</v>
@@ -10184,7 +10195,7 @@
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10199,29 +10210,29 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="K250" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>312</v>
+        <v>434</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10251,7 +10262,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10263,7 +10274,7 @@
         <v>290</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>315</v>
@@ -10286,7 +10297,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10306,7 +10317,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10321,7 +10332,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10330,10 +10341,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>314</v>
@@ -10369,7 +10380,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10378,7 +10389,7 @@
         <v>176</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I256" s="7">
         <v>36</v>
@@ -10389,7 +10400,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10404,22 +10415,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>176</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -10439,7 +10450,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10459,7 +10470,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10474,7 +10485,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10486,7 +10497,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>201</v>
@@ -10494,7 +10505,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10509,7 +10520,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10524,14 +10535,14 @@
         <v>186</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="K260" s="7">
         <v>332</v>
       </c>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>312</v>
+        <v>443</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10561,7 +10572,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10573,15 +10584,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10596,7 +10607,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10618,7 +10629,7 @@
       </c>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10633,7 +10644,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10645,7 +10656,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>21</v>
@@ -10655,7 +10666,7 @@
       </c>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10670,7 +10681,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10685,14 +10696,14 @@
         <v>199</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="K265" s="7">
         <v>308</v>
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10707,7 +10718,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10725,7 +10736,7 @@
         <v>71</v>
       </c>
       <c t="s" r="K266" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
@@ -10759,7 +10770,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10768,10 +10779,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>208</v>
@@ -10779,7 +10790,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10794,19 +10805,19 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>35</v>
@@ -10816,7 +10827,7 @@
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10831,7 +10842,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10843,17 +10854,17 @@
         <v>29</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="K270" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10868,7 +10879,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -10890,7 +10901,7 @@
       </c>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10905,7 +10916,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10914,10 +10925,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>185</v>
@@ -10925,7 +10936,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10940,13 +10951,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>17</v>
@@ -10960,7 +10971,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10990,7 +11001,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -11002,15 +11013,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -11025,7 +11036,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -11045,7 +11056,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -11060,7 +11071,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -11075,12 +11086,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11095,7 +11106,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -11107,15 +11118,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11130,7 +11141,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11142,15 +11153,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11165,7 +11176,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11177,17 +11188,17 @@
         <v>29</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c t="s" r="K280" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11217,7 +11228,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -11226,7 +11237,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>190</v>
@@ -11237,7 +11248,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11252,13 +11263,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>17</v>
@@ -11272,7 +11283,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11287,7 +11298,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -11296,7 +11307,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>315</v>
@@ -11307,7 +11318,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11322,22 +11333,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -11357,7 +11368,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -11366,7 +11377,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>229</v>
@@ -11377,7 +11388,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11392,19 +11403,19 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>23</v>
@@ -11429,7 +11440,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11441,7 +11452,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>275</v>
@@ -11451,7 +11462,7 @@
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11481,7 +11492,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11496,12 +11507,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11516,7 +11527,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11536,7 +11547,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11551,7 +11562,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11573,7 +11584,7 @@
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11588,7 +11599,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11603,14 +11614,14 @@
         <v>258</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11625,7 +11636,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11640,12 +11651,12 @@
         <v>55</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11660,7 +11671,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11695,7 +11706,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11707,10 +11718,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11743,7 +11754,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11752,10 +11763,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>321</v>
@@ -11763,7 +11774,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11778,13 +11789,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>17</v>
@@ -11798,7 +11809,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11813,7 +11824,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11828,12 +11839,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11848,7 +11859,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11860,7 +11871,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>174</v>
@@ -11870,7 +11881,7 @@
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11885,7 +11896,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11900,12 +11911,12 @@
         <v>164</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11920,7 +11931,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11932,15 +11943,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11955,7 +11966,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11967,7 +11978,7 @@
         <v>267</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>101</v>
@@ -11977,7 +11988,7 @@
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11992,7 +12003,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -12007,14 +12018,14 @@
         <v>42</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="K305" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -12044,7 +12055,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -12056,7 +12067,7 @@
         <v>219</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>64</v>
@@ -12064,7 +12075,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -12079,7 +12090,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -12091,7 +12102,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>268</v>
@@ -12099,7 +12110,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -12114,7 +12125,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12123,7 +12134,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>177</v>
@@ -12134,7 +12145,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12149,27 +12160,27 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -12184,7 +12195,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12196,10 +12207,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -12232,7 +12243,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12241,13 +12252,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -12267,19 +12278,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>171</v>
@@ -12287,7 +12298,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12302,7 +12313,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12311,13 +12322,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -12337,19 +12348,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>97</v>
@@ -12357,7 +12368,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12387,7 +12398,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12407,7 +12418,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12422,7 +12433,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12434,7 +12445,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>282</v>
@@ -12444,7 +12455,7 @@
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12459,7 +12470,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12468,7 +12479,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>272</v>
@@ -12477,11 +12488,11 @@
         <v>67</v>
       </c>
       <c t="s" r="K320" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12496,27 +12507,27 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12531,7 +12542,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12540,13 +12551,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>285</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12579,7 +12590,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12591,7 +12602,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>57</v>
@@ -12599,7 +12610,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12629,7 +12640,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12641,7 +12652,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>52</v>
@@ -12649,7 +12660,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12664,7 +12675,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12676,17 +12687,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>70</v>
       </c>
       <c t="s" r="K327" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12701,7 +12712,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12716,14 +12727,14 @@
         <v>23</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="K328" s="7">
         <v>101</v>
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12738,7 +12749,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12750,17 +12761,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12790,7 +12801,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12802,7 +12813,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>93</v>
@@ -12810,7 +12821,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12825,7 +12836,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12840,12 +12851,12 @@
         <v>328</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12860,7 +12871,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12880,7 +12891,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12895,7 +12906,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12910,7 +12921,7 @@
         <v>202</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12943,7 +12954,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12952,18 +12963,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12978,27 +12989,27 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -13013,7 +13024,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -13033,7 +13044,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -13048,7 +13059,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -13057,10 +13068,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>90</v>
@@ -13096,7 +13107,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -13105,7 +13116,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>27</v>
@@ -13116,7 +13127,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -13131,13 +13142,13 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
@@ -13146,7 +13157,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -13166,7 +13177,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -13175,18 +13186,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13201,27 +13212,27 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13236,7 +13247,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -13245,10 +13256,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>60</v>
@@ -13256,7 +13267,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13271,19 +13282,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>189</v>
@@ -13319,7 +13330,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -13331,7 +13342,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>255</v>
@@ -13354,7 +13365,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -13369,12 +13380,12 @@
         <v>177</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13389,7 +13400,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13409,7 +13420,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13424,7 +13435,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13433,18 +13444,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c t="s" r="I351" s="7">
         <v>212</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13459,22 +13470,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -13507,7 +13518,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13522,12 +13533,12 @@
         <v>208</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13557,7 +13568,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13569,7 +13580,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>321</v>
@@ -13577,7 +13588,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13592,7 +13603,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13612,7 +13623,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13627,7 +13638,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13642,7 +13653,7 @@
         <v>291</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13662,7 +13673,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -13674,7 +13685,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>94</v>
@@ -13682,7 +13693,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13697,7 +13708,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13712,12 +13723,12 @@
         <v>21</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13732,7 +13743,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13747,12 +13758,12 @@
         <v>182</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13767,7 +13778,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13776,18 +13787,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13802,13 +13813,13 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>29</v>
@@ -13817,7 +13828,7 @@
         <v>231</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13850,7 +13861,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13865,12 +13876,12 @@
         <v>31</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13885,7 +13896,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13897,15 +13908,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13920,7 +13931,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13932,7 +13943,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>19</v>
@@ -13940,7 +13951,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13955,7 +13966,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13970,7 +13981,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -14005,7 +14016,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -14025,7 +14036,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -14040,7 +14051,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -14060,7 +14071,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -14075,7 +14086,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -14087,15 +14098,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -14110,7 +14121,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14122,7 +14133,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>56</v>
@@ -14132,7 +14143,7 @@
       </c>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14162,7 +14173,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14174,7 +14185,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>224</v>
@@ -14182,7 +14193,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14197,7 +14208,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -14212,12 +14223,12 @@
         <v>192</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -14232,7 +14243,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -14269,7 +14280,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14287,11 +14298,11 @@
         <v>97</v>
       </c>
       <c t="s" r="K378" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14306,7 +14317,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14318,17 +14329,17 @@
         <v>219</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="K379" s="7">
         <v>168</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14343,7 +14354,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -14355,7 +14366,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>55</v>
@@ -14365,7 +14376,7 @@
       </c>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14380,7 +14391,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14389,20 +14400,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c t="s" r="K381" s="7">
         <v>212</v>
       </c>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14417,25 +14428,25 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c t="s" r="K382" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
@@ -14469,7 +14480,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14481,7 +14492,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>31</v>
@@ -14504,7 +14515,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14519,7 +14530,7 @@
         <v>266</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14539,7 +14550,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14551,7 +14562,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>269</v>
@@ -14559,7 +14570,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14574,7 +14585,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14583,20 +14594,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>99</v>
       </c>
       <c t="s" r="K387" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14611,13 +14622,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>17</v>
@@ -14626,14 +14637,14 @@
         <v>307</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c t="s" r="K388" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14648,7 +14659,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14660,17 +14671,17 @@
         <v>29</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c t="s" r="K389" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14685,7 +14696,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14697,7 +14708,7 @@
         <v>238</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>87</v>
@@ -14733,7 +14744,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14745,15 +14756,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14768,7 +14779,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14780,15 +14791,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14803,7 +14814,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14812,18 +14823,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="I394" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14838,13 +14849,13 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>29</v>
@@ -14858,7 +14869,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14873,7 +14884,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14895,7 +14906,7 @@
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14910,7 +14921,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14919,20 +14930,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c t="s" r="K397" s="7">
         <v>239</v>
       </c>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14947,29 +14958,29 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c t="s" r="K398" s="7">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14999,7 +15010,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -15011,7 +15022,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>31</v>
@@ -15034,7 +15045,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -15046,7 +15057,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>32</v>
@@ -15054,7 +15065,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -15069,7 +15080,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -15089,7 +15100,7 @@
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -15104,7 +15115,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -15116,7 +15127,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>210</v>
@@ -15124,7 +15135,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -15139,7 +15150,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -15151,7 +15162,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>181</v>
@@ -15174,7 +15185,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -15186,15 +15197,15 @@
         <v>219</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15209,7 +15220,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15221,17 +15232,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c t="s" r="K406" s="7">
         <v>185</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15261,7 +15272,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -15273,7 +15284,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>90</v>
@@ -15281,7 +15292,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15296,7 +15307,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -15308,7 +15319,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>20</v>
@@ -15316,7 +15327,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15331,7 +15342,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -15351,7 +15362,7 @@
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15366,7 +15377,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -15381,7 +15392,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -15414,13 +15425,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>29</v>
@@ -15434,7 +15445,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15449,7 +15460,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -15464,12 +15475,12 @@
         <v>227</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15484,7 +15495,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -15493,10 +15504,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>183</v>
@@ -15504,7 +15515,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15519,27 +15530,27 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15554,7 +15565,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -15566,7 +15577,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>36</v>
@@ -15602,7 +15613,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15622,7 +15633,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15637,7 +15648,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15649,7 +15660,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>173</v>
@@ -15657,7 +15668,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15672,7 +15683,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15684,15 +15695,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15707,7 +15718,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15727,7 +15738,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15742,7 +15753,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -15754,15 +15765,15 @@
         <v>176</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15792,7 +15803,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15807,12 +15818,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15827,7 +15838,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15847,7 +15858,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15862,7 +15873,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15877,12 +15888,12 @@
         <v>241</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15897,7 +15908,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -15917,7 +15928,7 @@
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15947,7 +15958,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -15962,12 +15973,12 @@
         <v>189</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15982,7 +15993,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
@@ -15991,18 +16002,18 @@
         <v>176</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c t="s" r="I431" s="7">
         <v>205</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -16017,13 +16028,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>219</v>
@@ -16032,12 +16043,12 @@
         <v>180</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -16067,13 +16078,13 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>38</v>
@@ -16082,14 +16093,14 @@
         <v>31</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="K434" s="7">
         <v>171</v>
       </c>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -16119,7 +16130,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="F436" s="7">
         <v>330</v>
@@ -16139,7 +16150,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16169,7 +16180,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -16181,7 +16192,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>35</v>
@@ -16189,7 +16200,7 @@
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -16204,7 +16215,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
@@ -16213,18 +16224,18 @@
         <v>176</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c t="s" r="I439" s="7">
         <v>180</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -16239,13 +16250,13 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>219</v>
@@ -16254,7 +16265,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -16287,7 +16298,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
@@ -16296,10 +16307,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>102</v>
@@ -16307,7 +16318,7 @@
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16322,19 +16333,19 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>189</v>
@@ -16342,7 +16353,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16372,7 +16383,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
@@ -16392,7 +16403,7 @@
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -16407,7 +16418,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -16427,7 +16438,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16442,7 +16453,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -16462,7 +16473,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16477,7 +16488,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
@@ -16486,10 +16497,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>191</v>
@@ -16529,27 +16540,27 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F450" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16564,7 +16575,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -16586,7 +16597,7 @@
       </c>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16601,7 +16612,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -16613,7 +16624,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>45</v>
@@ -16623,12 +16634,12 @@
       </c>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c t="s" r="A453" s="9">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -16648,7 +16659,7 @@
     <row r="454" ht="65.25" customHeight="1"/>
     <row r="455" ht="17.25" customHeight="1">
       <c t="s" r="A455" s="10">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -16661,7 +16672,7 @@
       <c r="J455" s="10"/>
       <c r="K455" s="10"/>
       <c t="s" r="L455" s="11">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M455" s="11"/>
       <c r="N455" s="11"/>
